--- a/healthcare_assessment_forms/011_nutrition_assessment_and_transition_plan--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/011_nutrition_assessment_and_transition_plan--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Dairy'}</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'gluten'}</t>
+          <t>gluten</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Gluten'}</t>
+          <t>Gluten</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'nuts'}</t>
+          <t>nuts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Nuts'}</t>
+          <t>Nuts</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'soy'}</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Soy'}</t>
+          <t>Soy</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fish'}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Shellfish'}</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'eggs'}</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Eggs'}</t>
+          <t>Eggs</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'crustaceans'}</t>
+          <t>crustaceans</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Crustaceans'}</t>
+          <t>Crustaceans</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'weight_loss'}</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Weight loss'}</t>
+          <t>Weight loss</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'weight_gain'}</t>
+          <t>weight_gain</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Weight gain'}</t>
+          <t>Weight gain</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'muscle_gain'}</t>
+          <t>muscle_gain</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Muscle gain'}</t>
+          <t>Muscle gain</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
